--- a/PAMF_DIG F2 - monthly2026-07-28.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-28.xlsx
@@ -6619,7 +6619,7 @@
         <v>0.09</v>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>0.09</v>
       </c>
       <c r="N166" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>0.09</v>
       </c>
       <c r="N294" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>0.09</v>
       </c>
       <c r="N324" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-28.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-28.xlsx
@@ -9612,7 +9612,7 @@
         <v>0.09</v>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>0.09</v>
       </c>
       <c r="N142" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>0.09</v>
       </c>
       <c r="N193" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>0.09</v>
       </c>
       <c r="N240" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>0.09</v>
       </c>
       <c r="N269" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>0.09</v>
       </c>
       <c r="N272" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
